--- a/GearSage-client/pkgGear/data_raw/mustad_hook_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/mustad_hook_import.xlsx
@@ -459,7 +459,7 @@
         <v/>
       </c>
       <c r="G2" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H2" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/grip_pin_big_bite_soft_plastics_hook.jpg</v>
@@ -494,7 +494,7 @@
         <v/>
       </c>
       <c r="G3" t="str">
-        <v>倒钓钩 / Drop Shot</v>
+        <v>倒钓钩</v>
       </c>
       <c r="H3" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/select_finesse_hook_1x_fine.jpg</v>
@@ -529,7 +529,7 @@
         <v/>
       </c>
       <c r="G4" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H4" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/kvd_grip_pin_soft_plastics_hook.jpg</v>
@@ -564,7 +564,7 @@
         <v/>
       </c>
       <c r="G5" t="str">
-        <v>倒钓钩 / Drop Shot</v>
+        <v>直柄钩</v>
       </c>
       <c r="H5" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/grip_pin_edge_finesse_soft_plastics_hook.jpg</v>
@@ -599,7 +599,7 @@
         <v/>
       </c>
       <c r="G6" t="str">
-        <v>倒钓钩 / Drop Shot</v>
+        <v>倒钓钩</v>
       </c>
       <c r="H6" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/double_wide_gap_dropshot_hook.png</v>
@@ -634,7 +634,7 @@
         <v/>
       </c>
       <c r="G7" t="str">
-        <v>倒钓钩 / Drop Shot</v>
+        <v>倒钓钩</v>
       </c>
       <c r="H7" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/dropshot_hook.jpg</v>
@@ -669,7 +669,7 @@
         <v/>
       </c>
       <c r="G8" t="str">
-        <v>倒钓钩 / Drop Shot</v>
+        <v>Wacky/Neko钩</v>
       </c>
       <c r="H8" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/titanx_wacky_neko_dropshot_hook.jpg</v>
@@ -704,7 +704,7 @@
         <v/>
       </c>
       <c r="G9" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H9" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/mega_bite_soft_plastics_hook.jpg</v>
@@ -739,7 +739,7 @@
         <v/>
       </c>
       <c r="G10" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H10" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/big_mouth_tube_hook.jpg</v>
@@ -774,7 +774,7 @@
         <v/>
       </c>
       <c r="G11" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H11" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/weighted_kvd_grip_pin_hook.jpg</v>
@@ -809,7 +809,7 @@
         <v/>
       </c>
       <c r="G12" t="str">
-        <v>特种钩 / Swimbait Hook</v>
+        <v>Swimbait钩</v>
       </c>
       <c r="H12" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/power_lock_plus_spring_keeper_hook_weighted.png</v>
@@ -844,7 +844,7 @@
         <v/>
       </c>
       <c r="G13" t="str">
-        <v>倒钓钩 / Wacky</v>
+        <v>Wacky/Neko钩</v>
       </c>
       <c r="H13" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/kvd_weedless_wacky_worm_hook.jpg</v>
@@ -879,7 +879,7 @@
         <v/>
       </c>
       <c r="G14" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H14" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/ultra_lock_soft_plastics_hook.jpg</v>
@@ -914,7 +914,7 @@
         <v/>
       </c>
       <c r="G15" t="str">
-        <v>倒钓钩 / Drop Shot</v>
+        <v>直柄钩</v>
       </c>
       <c r="H15" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/grip_pin_max_flippin_worm_hook_2x_strong.jpg</v>
@@ -949,7 +949,7 @@
         <v/>
       </c>
       <c r="G16" t="str">
-        <v>特种钩 / Bass Hook</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H16" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/impact_soft_plastics_hook_with_weedguard.jpg</v>
@@ -984,7 +984,7 @@
         <v/>
       </c>
       <c r="G17" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H17" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/kvd_grip_pin_hook_2x_fine.jpg</v>
@@ -1019,7 +1019,7 @@
         <v/>
       </c>
       <c r="G18" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H18" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/assault_wide_gap_hook.png</v>
@@ -1054,7 +1054,7 @@
         <v/>
       </c>
       <c r="G19" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H19" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/ultra_lock_soft_plastics_hook_1x_fine.jpg</v>
@@ -1089,7 +1089,7 @@
         <v/>
       </c>
       <c r="G20" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H20" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/offset_shank_worm_hook.jpg</v>
@@ -1124,7 +1124,7 @@
         <v/>
       </c>
       <c r="G21" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H21" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/assault_heavy_hook.png</v>
@@ -1159,7 +1159,7 @@
         <v/>
       </c>
       <c r="G22" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H22" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/alpha_grip_finesse_hook.jpg</v>
@@ -1194,7 +1194,7 @@
         <v/>
       </c>
       <c r="G23" t="str">
-        <v>倒钓钩 / Wacky</v>
+        <v>Wacky/Neko钩</v>
       </c>
       <c r="H23" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/weedless_titanx_wacky_neko_dropshot_hook.png</v>
@@ -1229,7 +1229,7 @@
         <v/>
       </c>
       <c r="G24" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>曲柄钩</v>
       </c>
       <c r="H24" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/impact_spring_keeper_hook.jpg</v>
@@ -1264,7 +1264,7 @@
         <v/>
       </c>
       <c r="G25" t="str">
-        <v>曲柄钩 / Offset / Wide Gap</v>
+        <v>直柄钩</v>
       </c>
       <c r="H25" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/impact_straight_keeper_hook.jpg</v>
@@ -1299,7 +1299,7 @@
         <v/>
       </c>
       <c r="G26" t="str">
-        <v>特种钩 / Bass Hook</v>
+        <v>Swimbait钩</v>
       </c>
       <c r="H26" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/MUSTAD_hooks/infiltrator_swim_hook.png</v>
